--- a/notebooks/CalSim3DeliveryDataExtractionInitFile_v1.xlsx
+++ b/notebooks/CalSim3DeliveryDataExtractionInitFile_v1.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27531"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E313B15A-7C3D-4DBC-AB2A-32DA815C8893}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8655977-13C8-4D12-942F-25ED6CF35FBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11,6 +11,7 @@
     <sheet name="Init" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -237,25 +238,25 @@
     <t>O47</t>
   </si>
   <si>
-    <t>A36</t>
-  </si>
-  <si>
-    <t>B36</t>
-  </si>
-  <si>
-    <t>C36</t>
-  </si>
-  <si>
-    <t>G36</t>
-  </si>
-  <si>
-    <t>H36</t>
-  </si>
-  <si>
-    <t>I36</t>
-  </si>
-  <si>
-    <t>J36</t>
+    <t>A39</t>
+  </si>
+  <si>
+    <t>B39</t>
+  </si>
+  <si>
+    <t>C39</t>
+  </si>
+  <si>
+    <t>G39</t>
+  </si>
+  <si>
+    <t>H39</t>
+  </si>
+  <si>
+    <t>I39</t>
+  </si>
+  <si>
+    <t>J39</t>
   </si>
 </sst>
 </file>

--- a/notebooks/CalSim3DeliveryDataExtractionInitFile_v1.xlsx
+++ b/notebooks/CalSim3DeliveryDataExtractionInitFile_v1.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27531"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8655977-13C8-4D12-942F-25ED6CF35FBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{887259F5-4437-469A-9090-E0D5B9DAD7A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -238,25 +238,25 @@
     <t>O47</t>
   </si>
   <si>
-    <t>A39</t>
-  </si>
-  <si>
-    <t>B39</t>
-  </si>
-  <si>
-    <t>C39</t>
-  </si>
-  <si>
-    <t>G39</t>
-  </si>
-  <si>
-    <t>H39</t>
-  </si>
-  <si>
-    <t>I39</t>
-  </si>
-  <si>
-    <t>J39</t>
+    <t>A40</t>
+  </si>
+  <si>
+    <t>B40</t>
+  </si>
+  <si>
+    <t>C40</t>
+  </si>
+  <si>
+    <t>G40</t>
+  </si>
+  <si>
+    <t>H40</t>
+  </si>
+  <si>
+    <t>I40</t>
+  </si>
+  <si>
+    <t>J40</t>
   </si>
 </sst>
 </file>

--- a/notebooks/CalSim3DeliveryDataExtractionInitFile_v1.xlsx
+++ b/notebooks/CalSim3DeliveryDataExtractionInitFile_v1.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27531"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{887259F5-4437-469A-9090-E0D5B9DAD7A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DEB952D-DD10-4926-836A-A0AAB7FB3F52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -232,31 +232,31 @@
     <t>cs3rpt2022_all_demand_units_v20251130.xlsx</t>
   </si>
   <si>
-    <t>E258</t>
-  </si>
-  <si>
     <t>O47</t>
   </si>
   <si>
-    <t>A40</t>
-  </si>
-  <si>
-    <t>B40</t>
-  </si>
-  <si>
-    <t>C40</t>
-  </si>
-  <si>
-    <t>G40</t>
-  </si>
-  <si>
-    <t>H40</t>
-  </si>
-  <si>
-    <t>I40</t>
-  </si>
-  <si>
-    <t>J40</t>
+    <t>E261</t>
+  </si>
+  <si>
+    <t>A46</t>
+  </si>
+  <si>
+    <t>B46</t>
+  </si>
+  <si>
+    <t>C46</t>
+  </si>
+  <si>
+    <t>G46</t>
+  </si>
+  <si>
+    <t>H46</t>
+  </si>
+  <si>
+    <t>I46</t>
+  </si>
+  <si>
+    <t>J46</t>
   </si>
 </sst>
 </file>
@@ -782,7 +782,7 @@
         <v>25</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -859,7 +859,7 @@
         <v>45</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E22" t="s">
         <v>63</v>

--- a/notebooks/CalSim3DeliveryDataExtractionInitFile_v1.xlsx
+++ b/notebooks/CalSim3DeliveryDataExtractionInitFile_v1.xlsx
@@ -3,15 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27531"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DEB952D-DD10-4926-836A-A0AAB7FB3F52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E098E9B-5E73-4838-A90C-D23D90C57F0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-2700" yWindow="-21720" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Init" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -235,9 +234,6 @@
     <t>O47</t>
   </si>
   <si>
-    <t>E261</t>
-  </si>
-  <si>
     <t>A46</t>
   </si>
   <si>
@@ -257,6 +253,9 @@
   </si>
   <si>
     <t>J46</t>
+  </si>
+  <si>
+    <t>E265</t>
   </si>
 </sst>
 </file>
@@ -653,7 +652,7 @@
         <v>7</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E5" s="2"/>
     </row>
@@ -668,7 +667,7 @@
         <v>34</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E6" s="2"/>
     </row>
@@ -683,7 +682,7 @@
         <v>19</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E7" s="2"/>
     </row>
@@ -698,7 +697,7 @@
         <v>20</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E8" s="2"/>
     </row>
@@ -713,7 +712,7 @@
         <v>21</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E9" s="2"/>
     </row>
@@ -728,7 +727,7 @@
         <v>22</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E10" s="2"/>
     </row>
@@ -743,7 +742,7 @@
         <v>36</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E11" s="2"/>
     </row>
@@ -782,7 +781,7 @@
         <v>25</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">

--- a/notebooks/CalSim3DeliveryDataExtractionInitFile_v1.xlsx
+++ b/notebooks/CalSim3DeliveryDataExtractionInitFile_v1.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27531"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E098E9B-5E73-4838-A90C-D23D90C57F0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6709D0A-46C6-4378-90B3-B38F6672F1D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-2700" yWindow="-21720" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1536" yWindow="1536" windowWidth="17280" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Init" sheetId="1" r:id="rId1"/>
@@ -255,7 +255,7 @@
     <t>J46</t>
   </si>
   <si>
-    <t>E265</t>
+    <t>E266</t>
   </si>
 </sst>
 </file>

--- a/notebooks/CalSim3DeliveryDataExtractionInitFile_v1.xlsx
+++ b/notebooks/CalSim3DeliveryDataExtractionInitFile_v1.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27531"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6709D0A-46C6-4378-90B3-B38F6672F1D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AC08DA3-62E7-4C9C-B506-A89E1737E560}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1536" yWindow="1536" windowWidth="17280" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Init" sheetId="1" r:id="rId1"/>
@@ -234,28 +234,28 @@
     <t>O47</t>
   </si>
   <si>
-    <t>A46</t>
-  </si>
-  <si>
-    <t>B46</t>
-  </si>
-  <si>
-    <t>C46</t>
-  </si>
-  <si>
-    <t>G46</t>
-  </si>
-  <si>
-    <t>H46</t>
-  </si>
-  <si>
-    <t>I46</t>
-  </si>
-  <si>
-    <t>J46</t>
-  </si>
-  <si>
     <t>E266</t>
+  </si>
+  <si>
+    <t>A49</t>
+  </si>
+  <si>
+    <t>B49</t>
+  </si>
+  <si>
+    <t>C49</t>
+  </si>
+  <si>
+    <t>G49</t>
+  </si>
+  <si>
+    <t>H49</t>
+  </si>
+  <si>
+    <t>I49</t>
+  </si>
+  <si>
+    <t>J49</t>
   </si>
 </sst>
 </file>
@@ -652,7 +652,7 @@
         <v>7</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E5" s="2"/>
     </row>
@@ -667,7 +667,7 @@
         <v>34</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E6" s="2"/>
     </row>
@@ -682,7 +682,7 @@
         <v>19</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E7" s="2"/>
     </row>
@@ -697,7 +697,7 @@
         <v>20</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E8" s="2"/>
     </row>
@@ -712,7 +712,7 @@
         <v>21</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E9" s="2"/>
     </row>
@@ -727,7 +727,7 @@
         <v>22</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E10" s="2"/>
     </row>
@@ -742,7 +742,7 @@
         <v>36</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E11" s="2"/>
     </row>
@@ -781,7 +781,7 @@
         <v>25</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">

--- a/notebooks/CalSim3DeliveryDataExtractionInitFile_v1.xlsx
+++ b/notebooks/CalSim3DeliveryDataExtractionInitFile_v1.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27531"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AC08DA3-62E7-4C9C-B506-A89E1737E560}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4B4B773-8496-49E4-995E-55F0362554B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -237,25 +237,25 @@
     <t>E266</t>
   </si>
   <si>
-    <t>A49</t>
-  </si>
-  <si>
-    <t>B49</t>
-  </si>
-  <si>
-    <t>C49</t>
-  </si>
-  <si>
-    <t>G49</t>
-  </si>
-  <si>
-    <t>H49</t>
-  </si>
-  <si>
-    <t>I49</t>
-  </si>
-  <si>
-    <t>J49</t>
+    <t>A25</t>
+  </si>
+  <si>
+    <t>B25</t>
+  </si>
+  <si>
+    <t>C25</t>
+  </si>
+  <si>
+    <t>G25</t>
+  </si>
+  <si>
+    <t>H25</t>
+  </si>
+  <si>
+    <t>I25</t>
+  </si>
+  <si>
+    <t>J25</t>
   </si>
 </sst>
 </file>
